--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486842_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486842_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3256</v>
+        <v>3.4375</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4733</v>
+        <v>7.9079</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.1476</v>
+        <v>-4.4704</v>
       </c>
       <c r="G2" t="n">
         <v>4.4066</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7226</v>
+        <v>-0.1655</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9647</v>
+        <v>0.3993</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.242</v>
+        <v>-0.5648</v>
       </c>
       <c r="V2" t="n">
         <v>1.5133</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3152</v>
+        <v>-0.0117</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5066</v>
+        <v>1.5618</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8218</v>
+        <v>-1.5735</v>
       </c>
       <c r="G3" t="n">
         <v>-1.501</v>
@@ -688,13 +688,13 @@
         <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9381</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1384</v>
+        <v>-0.0832</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7997</v>
+        <v>-0.5514</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.7133</v>
+        <v>-1.0625</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4213</v>
+        <v>-0.7456</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.292</v>
+        <v>-0.3168</v>
       </c>
       <c r="G4" t="n">
         <v>-2.2707</v>
@@ -766,13 +766,13 @@
         <v>0.5792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6784</v>
+        <v>-0.0275</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6347</v>
+        <v>0.0411</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0437</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1508</v>
+        <v>-2.0089</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4564</v>
+        <v>-0.091</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6944</v>
+        <v>-1.9179</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3605</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7558</v>
+        <v>-0.6138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8829</v>
+        <v>-0.5175</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1272</v>
+        <v>-0.0963</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.4335</v>
+        <v>-4.1124</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8448</v>
+        <v>-1.6505</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.2784</v>
+        <v>-2.4619</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1279</v>
+        <v>-2.6971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2963</v>
+        <v>-1.4898</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4242</v>
+        <v>-1.2072</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8108</v>
+        <v>0.3663</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2968</v>
+        <v>0.6489</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.486</v>
+        <v>-0.2826</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9387</v>
+        <v>-3.0634</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0005</v>
+        <v>-2.1387</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9382</v>
+        <v>-0.9247</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1239</v>
+        <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6284</v>
+        <v>-0.1104</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1579</v>
+        <v>0.4546</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5295</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.741</v>
+        <v>-1.8842</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.3129</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.741</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8862</v>
+        <v>-4.5449</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4988</v>
+        <v>-0.341</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3874</v>
+        <v>-4.2039</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6971</v>
+        <v>-1.1279</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4898</v>
+        <v>0.2963</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2072</v>
+        <v>-1.4242</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3663</v>
+        <v>1.8108</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6489</v>
+        <v>2.2968</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2826</v>
+        <v>-0.486</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0634</v>
+        <v>-2.9387</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1387</v>
+        <v>-2.0005</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9247</v>
+        <v>-0.9382</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1158</v>
+        <v>-0.483</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6063</v>
+        <v>-0.028</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4905</v>
+        <v>-0.455</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8842</v>
+        <v>-2.741</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.3129</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.0909</v>
+        <v>-4.8081</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9631</v>
+        <v>-1.8045</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1277</v>
+        <v>-3.0036</v>
       </c>
       <c r="G8" t="n">
         <v>-6.2631</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0209</v>
+        <v>-0.7381</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4142</v>
+        <v>-0.2556</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6067</v>
+        <v>-0.4825</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.9729</v>
+        <v>-5.3509</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1508</v>
+        <v>-2.5785</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8221</v>
+        <v>-2.7724</v>
       </c>
       <c r="G9" t="n">
         <v>-4.1525</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7392</v>
+        <v>-0.1172</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1936</v>
+        <v>0.3787</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5457</v>
+        <v>-0.496</v>
       </c>
       <c r="V9" t="n">
         <v>0.6565</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.3588</v>
+        <v>-6.5824</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5469</v>
+        <v>-3.9194</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8119</v>
+        <v>-2.6629</v>
       </c>
       <c r="G10" t="n">
         <v>-6.4472</v>
@@ -1234,13 +1234,13 @@
         <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1627</v>
+        <v>-1.3862</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1588</v>
+        <v>-0.5314</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0038</v>
+        <v>-0.8548</v>
       </c>
       <c r="V10" t="n">
         <v>0.2856</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-25.596</v>
+        <v>-25.0443</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2126</v>
+        <v>-1.660800000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-23.3833</v>
@@ -1312,10 +1312,10 @@
         <v>13.5154</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.8283</v>
+        <v>-4.2763</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6937000000000004</v>
+        <v>-0.142</v>
       </c>
       <c r="U11" t="n">
         <v>-4.1344</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.9959</v>
+        <v>8.341900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>7.7502</v>
+        <v>8.267300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2457</v>
+        <v>0.0745</v>
       </c>
       <c r="G12" t="n">
         <v>4.99</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>0.199</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2486</v>
+        <v>0.2685</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4476</v>
+        <v>0.2764</v>
       </c>
       <c r="V12" t="n">
         <v>1.8415</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6219</v>
+        <v>4.8915</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4019</v>
+        <v>2.6787</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2199</v>
+        <v>2.2128</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1273</v>
+        <v>4.6224</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4967</v>
+        <v>2.5516</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6307</v>
+        <v>2.0708</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4937</v>
+        <v>3.5548</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2902</v>
+        <v>1.7936</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2035</v>
+        <v>1.7612</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6337</v>
+        <v>1.0677</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2065</v>
+        <v>0.758</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4272</v>
+        <v>0.3096</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8574</v>
+        <v>-0.1171</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5647</v>
+        <v>0.0893</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2926</v>
+        <v>-0.2064</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2127</v>
+        <v>4.7616</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8449</v>
+        <v>3.7415</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3677</v>
+        <v>1.0201</v>
       </c>
       <c r="G14" t="n">
         <v>3.0721</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9821</v>
+        <v>0.5311</v>
       </c>
       <c r="T14" t="n">
-        <v>0.248</v>
+        <v>0.1446</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7341</v>
+        <v>0.3865</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7454</v>
+        <v>4.3229</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9547</v>
+        <v>2.954</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7907</v>
+        <v>1.3689</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6224</v>
+        <v>3.1273</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5516</v>
+        <v>2.4967</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0708</v>
+        <v>0.6307</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5548</v>
+        <v>2.4937</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7936</v>
+        <v>2.2902</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7612</v>
+        <v>0.2035</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0677</v>
+        <v>0.6337</v>
       </c>
       <c r="N15" t="n">
-        <v>0.758</v>
+        <v>0.2065</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3096</v>
+        <v>0.4272</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2632</v>
+        <v>1.5584</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6347</v>
+        <v>1.1168</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.4416</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7002</v>
+        <v>2.4808</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1495</v>
+        <v>2.3564</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4493</v>
+        <v>0.1244</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3479</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1876</v>
+        <v>0.593</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3859</v>
+        <v>0.5928</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5735</v>
+        <v>0.0002</v>
       </c>
       <c r="V16" t="n">
         <v>1.8842</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. HERNÁNDEZ CHÁVEZ</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.666</v>
+        <v>1.2921</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8612</v>
+        <v>0.6956</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8047</v>
+        <v>0.5965</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6301</v>
+        <v>1.7334</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0002</v>
+        <v>0.117</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6299</v>
+        <v>1.6163</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8448</v>
+        <v>0.2722</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3799</v>
+        <v>-0.5032</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4649</v>
+        <v>0.7754</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7853</v>
+        <v>1.4612</v>
       </c>
       <c r="N17" t="n">
         <v>0.6203</v>
       </c>
       <c r="O17" t="n">
-        <v>0.165</v>
+        <v>0.8409</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9088</v>
+        <v>0.5933</v>
       </c>
       <c r="T17" t="n">
-        <v>1.627</v>
+        <v>0.1378</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2818</v>
+        <v>0.4555</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9421</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
         <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2819</v>
+        <v>2.3284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.522</v>
+        <v>-1.5598</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7334</v>
+        <v>2.4375</v>
       </c>
       <c r="H18" t="n">
-        <v>0.117</v>
+        <v>1.1174</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6163</v>
+        <v>1.3202</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2722</v>
+        <v>4.0388</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5032</v>
+        <v>1.3938</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7754</v>
+        <v>2.645</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4612</v>
+        <v>-1.6012</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6203</v>
+        <v>-0.2764</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8409</v>
+        <v>-1.3248</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1051</v>
+        <v>0.331</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2759</v>
+        <v>0.2204</v>
       </c>
       <c r="U18" t="n">
-        <v>0.381</v>
+        <v>0.1107</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>S. SOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4707</v>
+        <v>0.5713</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6011</v>
+        <v>0.2605</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1304</v>
+        <v>0.3109</v>
       </c>
       <c r="G19" t="n">
-        <v>0.786</v>
+        <v>0.6677</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5728</v>
+        <v>1.511</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.8433</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0767</v>
+        <v>2.0065</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2629</v>
+        <v>1.9252</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8138</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2907</v>
+        <v>-1.3388</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6901</v>
+        <v>-0.4142</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6006</v>
+        <v>-0.9247</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1239</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8665</v>
+        <v>0.0621</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1928</v>
+        <v>0.2273</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6736</v>
+        <v>-0.1652</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9421</v>
+        <v>0.6138</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>-0.0426</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SOW</t>
+          <t>R. HERNÁNDEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4486</v>
+        <v>0.5572</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3639</v>
+        <v>-0.173</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0847</v>
+        <v>0.7302</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6677</v>
+        <v>2.6301</v>
       </c>
       <c r="H20" t="n">
-        <v>1.511</v>
+        <v>1.0002</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8433</v>
+        <v>1.6299</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0065</v>
+        <v>1.8448</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9252</v>
+        <v>0.3799</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>1.4649</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3388</v>
+        <v>0.7853</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4142</v>
+        <v>0.6203</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9247</v>
+        <v>0.165</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0606</v>
+        <v>0.8001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3307</v>
+        <v>0.5928</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3914</v>
+        <v>0.2073</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6138</v>
+        <v>-0.9421</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0426</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0458</v>
+        <v>0.4318</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3284</v>
+        <v>1.8079</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2826</v>
+        <v>-1.3761</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4375</v>
+        <v>0.786</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1174</v>
+        <v>1.5728</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3202</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0388</v>
+        <v>3.0767</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3938</v>
+        <v>2.2629</v>
       </c>
       <c r="L21" t="n">
-        <v>2.645</v>
+        <v>0.8138</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6012</v>
+        <v>-2.2907</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2764</v>
+        <v>-0.6901</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3248</v>
+        <v>-1.6006</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7723</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3917</v>
+        <v>0.8276</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2204</v>
+        <v>0.3997</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6121</v>
+        <v>0.428</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1149</v>
+        <v>-1.4447</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1544</v>
+        <v>-1.5338</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0395</v>
+        <v>0.0892</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3055</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1875</v>
+        <v>0.4827</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>0.3446</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1381</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6565</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>25.5962</v>
+        <v>26.975</v>
       </c>
       <c r="E23" t="n">
-        <v>23.3833</v>
+        <v>23.3835</v>
       </c>
       <c r="F23" t="n">
-        <v>2.212599999999999</v>
+        <v>3.5916</v>
       </c>
       <c r="G23" t="n">
         <v>22.4131</v>
@@ -2248,22 +2248,22 @@
         <v>11.5847</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8283</v>
+        <v>6.207100000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>4.1344</v>
+        <v>4.134600000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6935999999999999</v>
+        <v>2.0727</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2854999999999998</v>
+        <v>0.2855</v>
       </c>
       <c r="W23" t="n">
         <v>3.512500000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.226900000000001</v>
+        <v>-3.2269</v>
       </c>
     </row>
   </sheetData>
